--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:40</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-12 13:48:39</t>
+          <t>2026-09-13 14:44:42</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -582,11 +582,11 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -674,11 +674,11 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -766,11 +766,11 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -858,11 +858,11 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -950,11 +950,11 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1134,11 +1134,11 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>664</v>
+        <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1226,11 +1226,11 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1318,11 +1318,11 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1502,11 +1502,11 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1594,11 +1594,11 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1686,11 +1686,11 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Vacant Land / Acreage</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -1962,11 +1962,11 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2054,11 +2054,11 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>671</v>
+        <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2238,11 +2238,11 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>699</v>
+        <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2514,11 +2514,11 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2606,11 +2606,11 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2698,11 +2698,11 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2882,11 +2882,11 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -2974,11 +2974,11 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -3066,11 +3066,11 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -3158,11 +3158,11 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -3250,11 +3250,11 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tier 1: High Urgency (&lt; 45 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -3342,11 +3342,11 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Commercial / Mixed Use</t>
+          <t>Single Family Residential</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -3434,11 +3434,11 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>692</v>
+        <v>0</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -3526,11 +3526,11 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -3618,11 +3618,11 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>
@@ -3710,11 +3710,11 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
+          <t>Expired / Time-Barred</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>2026-09-13 14:44:42</t>
+          <t>2026-09-14 16:42:31</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,106 +425,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>County</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_Deadline_Date</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statute_Citation</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -582,31 +604,41 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -674,31 +706,41 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -766,31 +808,41 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -858,31 +910,41 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -950,31 +1012,41 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1051,22 +1123,32 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>2029-07-01</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1134,31 +1216,41 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1226,31 +1318,41 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1318,31 +1420,41 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1419,22 +1531,32 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>2029-08-12</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>https://www.cobbtax.org/</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1502,31 +1624,41 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1594,31 +1726,41 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1686,31 +1828,41 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1787,22 +1939,32 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
+          <t>2029-07-15</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1870,31 +2032,41 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -1962,31 +2134,41 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2054,31 +2236,41 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2146,31 +2338,41 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2238,31 +2440,41 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2486,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DeKalb</t>
+          <t>Dekalb</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2330,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2339,22 +2551,32 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>2029-08-05</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2422,31 +2644,41 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2514,31 +2746,41 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2606,31 +2848,41 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2698,31 +2950,41 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2790,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2799,22 +3061,32 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>2029-07-22</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2882,31 +3154,41 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -2974,31 +3256,41 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -3066,31 +3358,41 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>https://www.dallascounty.org/</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -3158,31 +3460,41 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -3250,31 +3562,41 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -3342,31 +3664,41 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -3434,31 +3766,41 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -3526,31 +3868,41 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -3618,31 +3970,41 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>
@@ -3710,31 +4072,41 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Expired / Time-Barred</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
+          <t>2026-11-30</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>2026-09-14 16:42:31</t>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-09-16 15:13:04</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-16 15:13:04</t>
+          <t>2026-09-17 15:22:30</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-17 15:22:30</t>
+          <t>2026-09-18 14:42:19</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-18 14:42:19</t>
+          <t>2026-09-19 14:03:02</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-19 14:03:02</t>
+          <t>2026-09-20 14:23:23</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-20 14:23:23</t>
+          <t>2026-09-21 16:42:18</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-21 16:42:18</t>
+          <t>2026-09-22 15:16:16</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-22 15:16:16</t>
+          <t>2026-09-23 15:14:48</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-23 15:14:48</t>
+          <t>2026-09-24 15:35:43</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:49</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-24 15:35:43</t>
+          <t>2026-09-25 15:40:48</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:49</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-25 15:40:48</t>
+          <t>2026-09-26 14:49:00</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-16</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-26 14:49:00</t>
+          <t>2026-09-27 15:27:36</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-11-17</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-27 15:27:36</t>
+          <t>2026-09-28 18:19:10</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-11-17</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-09-28 18:19:10</t>
+          <t>2026-09-29 12:50:34</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V36"/>
+  <dimension ref="A1:Y44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,100 +441,115 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Parcel_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Case_or_TaxDeed_No</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Owner_Name</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Entity_Type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Is_Individual</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Heir_Search_Recommended</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Property_Address</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Property_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Surplus_Balance_USD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Fee_Rate</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Est_Finder_Fee_USD</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Opportunity_Tier</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Sale_Date</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Days_Remaining_To_Claim</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Claim_Urgency_Tier</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Claim_Deadline_Date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Statutory_Deadline_Window</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Clerk_Verification_URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Governing_Statute</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Statute_Citation</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Record_Type</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>TYPE</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Enriched_Timestamp</t>
         </is>
@@ -553,92 +568,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2024-CA-008120</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>GREGORY &amp; EVELYN THATCHER</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
       <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>1420 WILSHIRE BLVD LOS ANGELES CA 90017</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>215000</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>43000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2024-07-09</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>50</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -655,92 +685,107 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2024-CA-005210</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>VICTOR &amp; MONICA REYES</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
       <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>4910 LA JOLLA BLVD SAN DIEGO CA 92037</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>184000</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>36800</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>50</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://www.sdttc.com/</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -757,92 +802,107 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2024-CA-008640</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ESTATE OF CAROLINE DELGADO</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Estate / Deceased</t>
         </is>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>3820 SUNSET BLVD LOS ANGELES CA 90026</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>168000</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>33600</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2024-07-30</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>50</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
           <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -859,806 +919,926 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>50-43-43-15-06-001-0020</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>2024-TD-004501</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>ANTHONY &amp; GRACE VALENTINE</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
       <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>720 S OCEAN BLVD PALM BEACH FL 33480</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>145000</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>29000</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>75</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-NC-003110</t>
+          <t>4942-12-05-0890</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DERRICK &amp; ANGELA MORGAN</t>
+          <t>2024-TD-003891</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>MARCUS &amp; HELENA VANDERBILT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
       <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>5820 SHARON RD CHARLOTTE NC 28210</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>1520 SE 12TH ST FORT LAUDERDALE FL 33316</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>138000</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>138500</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>27600</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>27700</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>50</v>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2024-07-19</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>N.C.G.S. § 105-374</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>N.C.G.S. § 105-374</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fulton</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-GA-003810</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MARCUS &amp; ELEANOR JENKINS</t>
+          <t>2024-NC-003110</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>DERRICK &amp; ANGELA MORGAN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
       <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1420 PEACHTREE ST NE ATLANTA GA 30309</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>5820 SHARON RD CHARLOTTE NC 28210</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>134000</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>138000</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>26800</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>27600</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024-07-02</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1006</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>50</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2029-07-01</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-TX-04812</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>WILLIAM &amp; MARY HOLLOWAY</t>
+          <t>2024-GA-003810</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>MARCUS &amp; ELEANOR JENKINS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
       <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>1420 PEACHTREE ST NE ATLANTA GA 30309</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>128500</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>32125</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>134000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>26800</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024-07-09</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>55</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1005</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+          <t>2029-07-01</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-TN-002190</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRANKLIN &amp; JUDITH MERCER</t>
+          <t>2024-TX-04812</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>WILLIAM &amp; MARY HOLLOWAY</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
       <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2418 WEST END AVE NASHVILLE TN 37203</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>5402 BRAESVALLEY DR HOUSTON TX 77096</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>126000</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>25200</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>128500</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>32125</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>50</v>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-CA-005780</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ESTATE OF DOUGLAS WINSLOW</t>
+          <t>2024-TN-002190</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
+          <t>FRANKLIN &amp; JUDITH MERCER</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2104 CORONADO AVE SAN DIEGO CA 92154</t>
-        </is>
+      <c r="H10" t="b">
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>2418 WEST END AVE NASHVILLE TN 37203</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>119500</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>126000</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>23900</v>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="n">
+        <v>25200</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>50</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+          <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cobb</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-GA-001550</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ESTATE OF RAYMOND VAUGHN</t>
+          <t>2024-CA-005780</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>ESTATE OF DOUGLAS WINSLOW</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
       </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1205 ROSWELL RD MARIETTA GA 30062</t>
-        </is>
+      <c r="H11" t="b">
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>2104 CORONADO AVE SAN DIEGO CA 92154</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>118000</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>119500</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>23600</v>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="n">
+        <v>23900</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>1048</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>50</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2029-08-12</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>1 Year from Deed Recording (Cal. Rev. &amp; Tax Code § 4675)</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Cal. Rev. &amp; Tax Code § 4675</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Cobb</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-NC-001420</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HARRISON &amp; CAROLINE VANCE</t>
+          <t>2024-GA-001550</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
+          <t>ESTATE OF RAYMOND VAUGHN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4210 GLENWOOD AVE RALEIGH NC 27612</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>1205 ROSWELL RD MARIETTA GA 30062</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>114500</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>118000</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>22900</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" t="n">
+        <v>23600</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>50</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1047</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
+          <t>2029-08-12</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>N.C.G.S. § 105-374</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>N.C.G.S. § 105-374</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -1675,500 +1855,575 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-TD-004812</t>
+          <t>02-3209-018-0240</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LUIS &amp; MARIA HERNANDEZ</t>
+          <t>2024-CA-012874</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F13" t="b">
-        <v>1</v>
+          <t>ESTATE OF JULIAN MERCER</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>340 SW 8TH ST MIAMI FL 33130</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Single Family Residential</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>112000</v>
-      </c>
-      <c r="K13" t="inlineStr">
+          <t>1440 OCEAN DR APT 402 MIAMI BEACH FL 33139</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Condo / Multi-Family</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>115000</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="n">
+        <v>23000</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024-08-05</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>75</v>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Fla. Stat. § 197.582</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shelby</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-TN-004110</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAWRENCE &amp; TINA BENNETT</t>
+          <t>2024-NC-001420</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>HARRISON &amp; CAROLINE VANCE</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
       <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1720 POPLAR AVE MEMPHIS TN 38104</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>4210 GLENWOOD AVE RALEIGH NC 27612</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>102000</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>114500</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>20400</v>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="n">
+        <v>22900</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>50</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fulton</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-GA-004120</t>
+          <t>01-4138-005-0120</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESTATE OF HAROLD CRAWFORD</t>
+          <t>2024-TD-004812</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F15" t="b">
-        <v>1</v>
+          <t>LUIS &amp; MARIA HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>892 CASCADE AVE SW ATLANTA GA 30310</t>
-        </is>
+      <c r="H15" t="b">
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>340 SW 8TH ST MIAMI FL 33130</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>96500</v>
-      </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>112000</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>19300</v>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="M15" t="n">
+        <v>22400</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>1020</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>75</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2029-07-15</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mecklenburg</t>
+          <t>Shelby</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-NC-003450</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESTATE OF WALTER STERLING</t>
+          <t>2024-TN-004110</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
+          <t>LAWRENCE &amp; TINA BENNETT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2910 PROVIDENCE RD CHARLOTTE NC 28211</t>
-        </is>
+      <c r="H16" t="b">
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>1720 POPLAR AVE MEMPHIS TN 38104</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>96400</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>102000</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>19280</v>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="M16" t="n">
+        <v>20400</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
         <v>50</v>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>N.C.G.S. § 105-374</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>N.C.G.S. § 105-374</t>
+          <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-TD-008912</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
+          <t>2024-GA-004120</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F17" t="b">
-        <v>1</v>
+          <t>ESTATE OF HAROLD CRAWFORD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>892 CASCADE AVE SW ATLANTA GA 30310</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>92400</v>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>96500</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>18480</v>
-      </c>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="n">
+        <v>19300</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024-07-25</t>
-        </is>
-      </c>
-      <c r="O17" t="n">
-        <v>75</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1019</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2029-07-15</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -2180,403 +2435,463 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wake</t>
+          <t>Mecklenburg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-NC-001890</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ESTATE OF SAMUEL KAUFMAN</t>
+          <t>2024-NC-003450</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>ESTATE OF WALTER STERLING</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
       </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1804 FALLS OF NEUSE RD RALEIGH NC 27609</t>
-        </is>
+      <c r="H18" t="b">
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>2910 PROVIDENCE RD CHARLOTTE NC 28211</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>88200</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>96400</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>17640</v>
-      </c>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="n">
+        <v>19280</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
         <v>50</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Hillsborough</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-TX-04950</t>
+          <t>182914-4TA000001000020</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ESTATE OF CHARLES BEAUMONT</t>
+          <t>2024-TD-008912</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
+          <t>ROBERT &amp; CLAIRE SULLIVAN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
-        </is>
+      <c r="H19" t="b">
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>4502 W SAN RAFAEL ST TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>86200</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>21550</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>92400</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>18480</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>55</v>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Miami-Dade</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-TN-002840</t>
+          <t>30-4014-012-0580</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ESTATE OF GLORIA CHANDLER</t>
+          <t>2024-CA-014289</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>ESTATE OF VICTORIA CRANE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
       </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>3904 GALLATIN PIKE NASHVILLE TN 37216</t>
-        </is>
+      <c r="H20" t="b">
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>10845 SW 72ND AVE MIAMI FL 33156</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>84500</v>
-      </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>89450</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>16900</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="n">
+        <v>17890</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="O20" t="n">
-        <v>50</v>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dekalb</t>
+          <t>Wake</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-GA-002490</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TERRENCE &amp; MONICA BRADLEY</t>
+          <t>2024-NC-001890</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
+          <t>ESTATE OF SAMUEL KAUFMAN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2340 LAVISTA RD DECATUR GA 30033</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>1804 FALLS OF NEUSE RD RALEIGH NC 27609</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>82400</v>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>88200</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>16480</v>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="n">
+        <v>17640</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>1041</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>50</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2029-08-05</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -2588,607 +2903,697 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-TX-02044</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ESTATE OF MARGARET THORNTON</t>
+          <t>2024-TX-04950</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>ESTATE OF CHARLES BEAUMONT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
       </c>
-      <c r="F22" t="b">
-        <v>1</v>
-      </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>6412 ABRAMS RD DALLAS TX 75231</t>
-        </is>
+      <c r="H22" t="b">
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>1802 HEIGHTS BLVD HOUSTON TX 77008</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>77800</v>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>86200</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>19450</v>
-      </c>
-      <c r="M22" t="inlineStr">
+      <c r="M22" t="n">
+        <v>21550</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
         <v>55</v>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>https://www.dallascounty.org/</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
+          <t>https://www.hcdistrictclerk.com/</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-TD-001955</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>JAMES &amp; LINDA CHEN</t>
+          <t>2024-TN-002840</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F23" t="b">
-        <v>1</v>
+          <t>ESTATE OF GLORIA CHANDLER</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>3904 GALLATIN PIKE NASHVILLE TN 37216</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>74300</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="n">
+        <v>84500</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>14860</v>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="M23" t="n">
+        <v>16900</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2024-08-08</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>75</v>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shelby</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-TN-004550</t>
+          <t>5142-28-03-0140</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ESTATE OF BERNARD HAYES</t>
+          <t>2024-TD-004105</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>ESTATE OF RAYMOND CHANDLER</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
       </c>
-      <c r="F24" t="b">
-        <v>1</v>
-      </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>4810 PARK AVE MEMPHIS TN 38117</t>
-        </is>
+      <c r="H24" t="b">
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>3840 N 56TH AVE HOLLYWOOD FL 33021</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>71800</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="n">
+        <v>84200</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>14360</v>
-      </c>
-      <c r="M24" t="inlineStr">
+      <c r="M24" t="n">
+        <v>16840</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>50</v>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2024-08-01</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>T.C.A. § 67-5-2501</t>
+          <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palm Beach</t>
+          <t>Dekalb</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-TD-004688</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ESTATE OF ARTHUR STERLING</t>
+          <t>2024-GA-002490</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F25" t="b">
-        <v>1</v>
+          <t>TERRENCE &amp; MONICA BRADLEY</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
-        </is>
+      <c r="H25" t="b">
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>2340 LAVISTA RD DECATUR GA 30033</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>68900</v>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="n">
+        <v>82400</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>13780</v>
-      </c>
-      <c r="M25" t="inlineStr">
+      <c r="M25" t="n">
+        <v>16480</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>75</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>1040</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2029-08-05</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Gwinnett</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-GA-001920</t>
+          <t>00-43-43-05-11-002-0080</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VICTORIA STRICKLAND</t>
+          <t>2024-CA-006731</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>REBECCA &amp; GERALD MONROE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F26" t="b">
-        <v>1</v>
-      </c>
       <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="b">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>4510 LAWRENCEVILLE HWY LILBURN GA 30047</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>318 COLONIAL RD WEST PALM BEACH FL 33405</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>67800</v>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" t="n">
+        <v>78250</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>13560</v>
-      </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" t="n">
+        <v>15650</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>1027</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
-        </is>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>105</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2029-07-22</t>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>O.C.G.A. § 48-4-5</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Durham</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-NC-002100</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PATRICIA HOLLOWAY</t>
+          <t>2024-TX-02044</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F27" t="b">
-        <v>1</v>
+          <t>ESTATE OF MARGARET THORNTON</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>1408 DUKE UNIVERSITY RD DURHAM NC 27701</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>6412 ABRAMS RD DALLAS TX 75231</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>64500</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>12900</v>
-      </c>
-      <c r="M27" t="inlineStr">
+      <c r="K27" t="n">
+        <v>77800</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>19450</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2024-07-11</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>50</v>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>2026-11-18</t>
-        </is>
-      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>N.C.G.S. § 105-374</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>N.C.G.S. § 105-374</t>
+          <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -3205,194 +3610,224 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-TD-001501</t>
+          <t>28-23-27-0000-00-015</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ESTATE OF ELEANOR VANCE</t>
+          <t>2024-TD-001955</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Estate / Deceased</t>
-        </is>
-      </c>
-      <c r="F28" t="b">
-        <v>1</v>
+          <t>JAMES &amp; LINDA CHEN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
-        </is>
+      <c r="H28" t="b">
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>8431 BAY BREEZE WAY ORLANDO FL 32836</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>61800</v>
-      </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="n">
+        <v>74300</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>12360</v>
-      </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" t="n">
+        <v>14860</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
         <v>75</v>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Shelby</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-TX-01928</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GEORGE &amp; DOROTHY WASHINGTON</t>
+          <t>2024-TN-004550</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F29" t="b">
-        <v>1</v>
+          <t>ESTATE OF BERNARD HAYES</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G29" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>3819 COLONIAL AVE DALLAS TX 75215</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
+          <t>4810 PARK AVE MEMPHIS TN 38117</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>59400</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>14850</v>
-      </c>
-      <c r="M29" t="inlineStr">
+      <c r="K29" t="n">
+        <v>71800</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>14360</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>55</v>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>Chancery Court Motion Procedure (T.C.A. § 67-5-2501)</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>T.C.A. § 67-5-2501</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>T.C.A. § 67-5-2501</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -3404,199 +3839,229 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Palm Beach</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-TD-009041</t>
+          <t>00-42-43-27-05-022-0140</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ESTATE OF HENRY PATTERSON</t>
+          <t>2024-TD-004688</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>ESTATE OF ARTHUR STERLING</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>Estate / Deceased</t>
         </is>
       </c>
-      <c r="F30" t="b">
-        <v>1</v>
-      </c>
       <c r="G30" t="b">
         <v>1</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
-        </is>
+      <c r="H30" t="b">
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>1410 N FEDERAL HWY LAKE WORTH FL 33460</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>54100</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="n">
+        <v>68900</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>10820</v>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" t="n">
+        <v>13780</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2024-08-02</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
         <v>75</v>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>https://www.hillsclerk.com/</t>
-        </is>
-      </c>
       <c r="T30" t="inlineStr">
         <is>
+          <t>https://www.mypalmbeachclerk.com/</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Gwinnett</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-TD-001248</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RICHARD HAWKINS</t>
+          <t>2024-GA-001920</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>VICTORIA STRICKLAND</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
       <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="b">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>4510 LAWRENCEVILLE HWY LILBURN GA 30047</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>48250</v>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" t="n">
+        <v>67800</v>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>9650</v>
-      </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" t="n">
+        <v>13560</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2024-06-12</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>75</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Tier 2: Priority Window (45–120 Days)</t>
-        </is>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1026</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>Tier 3: Active Claim Window (&gt; 120 Days)</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2029-07-22</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>5 Years from Sale (O.C.G.A. § 48-4-5)</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>O.C.G.A. § 48-4-5</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>O.C.G.A. § 48-4-5</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -3608,199 +4073,229 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Miami-Dade</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-TD-004990</t>
+          <t>4842-18-09-0410</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EUGENE FITZPATRICK</t>
+          <t>2024-CA-009842</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
+          <t>ESTATE OF LAWRENCE THORNE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>1920 CORAL WAY MIAMI FL 33145</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>4210 NE 22ND AVE LIGHTHOUSE POINT FL 33064</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>43500</v>
-      </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="n">
+        <v>64800</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>8700</v>
-      </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" t="n">
+        <v>12960</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>75</v>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2027-01-13</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Fla. Stat. § 45.032</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Durham</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-TX-05110</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>RAFAEL GUERRERO</t>
+          <t>2024-NC-002100</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>PATRICIA HOLLOWAY</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
       <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="b">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>1408 DUKE UNIVERSITY RD DURHAM NC 27701</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>41300</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>10325</v>
-      </c>
-      <c r="M33" t="inlineStr">
+      <c r="K33" t="n">
+        <v>64500</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>12900</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>55</v>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2024-07-11</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>2026-11-23</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>10-Day Upset Bid / Judicial Registry (N.C.G.S. § 105-374)</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Tex. Tax Code § 34.04</t>
+          <t>N.C.G.S. § 105-374</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>N.C.G.S. § 105-374</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -3812,199 +4307,229 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hillsborough</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-TD-009188</t>
+          <t>29-22-30-0000-00-042</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DANIELLE KAUFMAN</t>
+          <t>2024-TD-001501</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Individual / Estate</t>
-        </is>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
+          <t>ESTATE OF ELEANOR VANCE</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
       </c>
       <c r="G34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>3309 ROSEWOOD CT WINTER PARK FL 32792</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>31750</v>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>61800</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>6350</v>
-      </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" t="n">
+        <v>12360</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2024-08-10</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
         <v>75</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R34" t="inlineStr">
         <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>https://www.hillsclerk.com/</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-TD-001622</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+          <t>2024-TX-01928</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>GEORGE &amp; DOROTHY WASHINGTON</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F35" t="b">
-        <v>1</v>
-      </c>
       <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="b">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
+          <t>3819 COLONIAL AVE DALLAS TX 75215</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>29400</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>5880</v>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>59400</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>14850</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>Tier 1: High Value ($25k+)</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>75</v>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Fla. Stat. § 197.582</t>
+          <t>Tex. Tax Code § 34.04</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-09-29 12:50:34</t>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>
@@ -4016,97 +4541,1048 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>192802-5TB000002000040</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2024-TD-009041</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ESTATE OF HENRY PATTERSON</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Estate / Deceased</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11804 N 56TH ST TEMPLE TERRACE FL 33617</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>54100</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>10820</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Broward</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4842-35-08-0320</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2024-TD-002980</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PATRICIA &amp; GLENN O'CONNOR</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2100 NE 48TH ST POMPANO BEACH FL 33064</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>52700</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>10540</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Orange</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>29-22-29-0000-00-088</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2024-TD-001248</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RICHARD HAWKINS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1420 PINEWOOD DR ORLANDO FL 32808</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>48250</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>9650</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Miami-Dade</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>01-3122-015-0450</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2024-TD-004990</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>EUGENE FITZPATRICK</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1920 CORAL WAY MIAMI FL 33145</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>43500</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>8700</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>https://www.miamidadeclerk.gov/</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Broward</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5041-35-02-0190</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2024-CA-011205</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>THOMAS &amp; CLARA WHITFIELD</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>8920 SW 18TH ST PLANTATION FL 33324</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>41600</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>8320</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>60 Days from Certificate of Disbursement (Fla. Stat. § 45.032)</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>https://www.browardclerk.org/</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 45.032</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Foreclosure Surplus</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>FORECLOSURE</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2024-TX-05110</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAFAEL GUERRERO</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7120 NAVIGATION BLVD HOUSTON TX 77011</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>41300</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>10325</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2024-08-06</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-11-24</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2 Years from Sale (Tex. Tax Code § 34.04)</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>https://www.hcdistrictclerk.com/</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Tex. Tax Code § 34.04</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Hillsborough</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>182923-3TC000001000010</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2024-TD-009188</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DANIELLE KAUFMAN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2308 S ARMENIA AVE TAMPA FL 33629</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>31750</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>6350</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>https://www.hillsclerk.com/</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>28-21-15-0000-00-031</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2024-TD-001622</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MARCOS &amp; SOFIA ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Individual / Estate</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>510 LAKE BREEZE DR APOPKA FL 32703</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Single Family Residential</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>29400</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>5880</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tier 1: High Value ($25k+)</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Tier 2: Priority Window (45–120 Days)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>https://www.myorangeclerk.com/</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 197.582</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>29-23-35-0000-00-019</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>2024-TD-001844</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>BEATRICE MONTGOMERY</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Individual / Estate</t>
         </is>
       </c>
-      <c r="F36" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" t="b">
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
+      <c r="H44" t="b">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>220 W KALEY ST ORLANDO FL 32806</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Single Family Residential</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K44" t="n">
         <v>18900</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="L36" t="n">
+      <c r="M44" t="n">
         <v>3780</v>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Tier 2: Medium Value ($10k-$25k)</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>2024-08-01</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="P44" t="n">
         <v>75</v>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Tier 2: Priority Window (45–120 Days)</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>2026-12-13</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-12-14</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
         <is>
           <t>120 Days from Notice (Fla. Stat. § 197.582)</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>Fla. Stat. § 197.582</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>2026-09-29 12:50:34</t>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Tax Deed Surplus</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>TAX_DEED</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:32:16</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2027-01-14</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-30 12:32:16</t>
+          <t>2026-10-01 13:10:51</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-14</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-01 13:10:51</t>
+          <t>2026-10-02 12:32:01</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-15</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-02 12:32:01</t>
+          <t>2026-10-03 11:37:45</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2027-01-17</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-03 11:37:45</t>
+          <t>2026-10-04 12:19:33</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-17</t>
+          <t>2027-01-18</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-04 12:19:33</t>
+          <t>2026-10-05 14:34:20</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-25</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-18</t>
+          <t>2027-01-19</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-05 14:34:20</t>
+          <t>2026-10-06 13:16:59</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-19</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-06 13:16:59</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-22</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-08 13:26:31</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-21</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-22</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-08 13:26:31</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008120</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005210</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008640</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003110</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002190</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005780</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001420</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004110</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003450</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001890</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002840</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004550</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>https://www.nccourts.gov/locations/durham?docket=2024-NC-002100</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-09 13:14:18</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008120</t>
+          <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005210</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/tax-defaulted-property-sales/?docket=2024-CA-008640</t>
+          <t>https://ttc.lacounty.gov/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003110</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-003810</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002190</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/content/ttc/en/tax-collection/tax-sale.html?docket=2024-CA-005780</t>
+          <t>https://www.sdttc.com/</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/excess-funds?docket=2024-GA-001550</t>
+          <t>https://www.cobbtax.org/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-012874</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001420</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004812</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004110</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/case-search?docket=2024-GA-004120</t>
+          <t>https://www.fultonclerk.org/</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg?docket=2024-NC-003450</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-008912</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www2.miamidadeclerk.gov/ocs/Search.aspx?caseNumber=2024-CA-014289</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake/wake-county-clerk-of-superior-court?docket=2024-NC-001890</t>
+          <t>https://www.nccourts.gov/locations/wake</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/case-search?docket=2024-TN-002840</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
+          <t>https://www.dekalbcountytax.org/</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-02044</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001955</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/case-search?docket=2024-TN-004550</t>
+          <t>https://chancery.shelbycountytn.gov/</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
+          <t>https://www.mypalmbeachclerk.com/</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/excess-funds?docket=2024-GA-001920</t>
+          <t>https://www.gwinnetttaxcommissioner.com/</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-26</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham?docket=2024-NC-002100</t>
+          <t>https://www.nccourts.gov/locations/durham</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001501</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/government/district-clerk/tax-foreclosures.php?case=2024-TX-01928</t>
+          <t>https://www.dallascounty.org/</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009041</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001248</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/clerk/tax-deeds.page?caseNumber=2024-TD-004990</t>
+          <t>https://www.miamidadeclerk.gov/</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
+          <t>https://www.browardclerk.org/</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
+          <t>https://www.hcdistrictclerk.com/</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/Court-Services/Tax-Deeds?caseNumber=2024-TD-009188</t>
+          <t>https://www.hillsclerk.com/</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001622</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://myclerk.myorangeclerk.com/Case/CaseDetails?caseNumber=2024-TD-001844</t>
+          <t>https://www.myorangeclerk.com/</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-09 13:14:18</t>
+          <t>2026-10-07 13:20:07</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/notice-of-excess-proceeds/?docket=2024-CA-008120</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/property-tax-sales.html?docket=2024-CA-005210</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://ttc.lacounty.gov/</t>
+          <t>https://ttc.lacounty.gov/notice-of-excess-proceeds/?docket=2024-CA-008640</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004501</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-003891</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg-county?docket=2024-NC-003110</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-003810</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04812</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/cases/public-records-search/?docket=2024-TN-002190</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.sdttc.com/</t>
+          <t>https://www.sdttc.com/content/ttc/en/tax-collection/property-tax-sales.html?docket=2024-CA-005780</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.cobbtax.org/</t>
+          <t>https://www.cobbtax.org/property/tax_sale/index.php?docket=2024-GA-001550</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-012874</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake-county?docket=2024-NC-001420</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004812</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://www.shelbycountytn.gov/222/Chancery-Court?docket=2024-TN-004110</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>https://www.fultonclerk.org/</t>
+          <t>https://www.fultonclerk.org/536/Records-Search-Center?docket=2024-GA-004120</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/mecklenburg</t>
+          <t>https://www.nccourts.gov/locations/mecklenburg-county?docket=2024-NC-003450</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-008912</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www2.miamidadeclerk.gov/QOS/default.aspx?caseNumber=2024-CA-014289</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/wake</t>
+          <t>https://www.nccourts.gov/locations/wake-county?docket=2024-NC-001890</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-04950</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://chanceryclerkandmaster.nashville.gov/</t>
+          <t>https://chanceryclerkandmaster.nashville.gov/cases/public-records-search/?docket=2024-TN-002840</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-004105</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>https://www.dekalbcountytax.org/</t>
+          <t>https://www.dekalbcountytax.org/excess-funds?docket=2024-GA-002490</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-CA-006731</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-02044</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001955</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://chancery.shelbycountytn.gov/</t>
+          <t>https://www.shelbycountytn.gov/222/Chancery-Court?docket=2024-TN-004550</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>https://www.mypalmbeachclerk.com/</t>
+          <t>https://www.mypalmbeachclerk.com/casesearch?caseNumber=2024-TD-004688</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>https://www.gwinnetttaxcommissioner.com/</t>
+          <t>https://www.gwinnetttaxcommissioner.com/property-tax/tax-sale-excess-funds?docket=2024-GA-001920</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-009842</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-26</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://www.nccourts.gov/locations/durham</t>
+          <t>https://www.nccourts.gov/locations/durham-county?docket=2024-NC-002100</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001501</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://www.dallascounty.org/</t>
+          <t>https://www.dallascounty.org/government/county-clerk/recording/foreclosures.php?case=2024-TX-01928</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009041</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Divisions/TaxDeeds?caseNumber=2024-TD-002980</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001248</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>https://www.miamidadeclerk.gov/</t>
+          <t>https://www.miamidadeclerk.gov/clerk/property-tax-deeds.page?caseNumber=2024-TD-004990</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2027-01-23</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.browardclerk.org/</t>
+          <t>https://www.browardclerk.org/Web2/CaseSearch/Details/?caseNumber=2024-CA-011205</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.hcdistrictclerk.com/</t>
+          <t>https://www.hcdistrictclerk.com/edocs/public/CaseDetails.aspx?Cas=2024-TX-05110</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.hillsclerk.com/</t>
+          <t>https://www.hillsclerk.com/taxdeeds?caseNumber=2024-TD-009188</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001622</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-24</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://www.myorangeclerk.com/</t>
+          <t>https://myeclerk.myorangeclerk.com/?caseNumber=2024-TD-001844</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-07 13:20:07</t>
+          <t>2026-10-10 12:29:43</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-23</t>
+          <t>2027-01-24</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026-12-25</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-10 12:29:43</t>
+          <t>2026-10-11 12:47:01</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-24</t>
+          <t>2027-01-25</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-05</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-25</t>
+          <t>2026-12-26</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-11 12:47:01</t>
+          <t>2026-10-12 15:20:46</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-25</t>
+          <t>2027-01-26</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-06</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-26</t>
+          <t>2026-12-27</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-12 15:20:46</t>
+          <t>2026-10-13 14:09:08</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-26</t>
+          <t>2027-01-27</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-12-08</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-27</t>
+          <t>2026-12-28</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-13 14:09:08</t>
+          <t>2026-10-14 11:49:35</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-27</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-08</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-14 11:49:35</t>
+          <t>2026-10-15 11:26:20</t>
         </is>
       </c>
     </row>

--- a/exports/Master_Surplus_Lead_Feed.xlsx
+++ b/exports/Master_Surplus_Lead_Feed.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-05</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2026-12-30</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-15 11:26:20</t>
+          <t>2026-10-16 11:20:53</t>
         </is>
       </c>
     </row>
